--- a/patternSystems/Test Worksheet.xlsx
+++ b/patternSystems/Test Worksheet.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacob\Documents\Programming Projects\InterpolationDraping\InterpolationDraping\patternSystems\ProofOfConcept\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacob\Documents\Programming Projects\InterpolationDraping\InterpolationDraping\patternSystems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82130A78-B20B-4D51-8BFA-C4D40C3F9518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09C778B-DEF3-4B18-8CB2-0E57D3C10FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13749" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3456" yWindow="1978" windowWidth="18031" windowHeight="9843" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="1" r:id="rId1"/>
-    <sheet name="ComputerOutput" sheetId="2" r:id="rId2"/>
-    <sheet name="Pattern Details" sheetId="3" r:id="rId3"/>
+    <sheet name="Pattern Details" sheetId="3" r:id="rId2"/>
+    <sheet name="Drafting Instructions" sheetId="4" r:id="rId3"/>
+    <sheet name="ComputerOutput" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Points</t>
   </si>
@@ -66,6 +67,18 @@
   </si>
   <si>
     <t>Line</t>
+  </si>
+  <si>
+    <t>This page of the program is an explanation of the demo.</t>
+  </si>
+  <si>
+    <t>The next page is the user interface, where the user  will enter the measurements.</t>
+  </si>
+  <si>
+    <t>The next page is human readable output, if you wish to hand draft the final product.</t>
+  </si>
+  <si>
+    <t>The final page is the computer output, which is read into the computer program when activated. This Excel file needs to be saved for the changes to be read by the program.</t>
   </si>
 </sst>
 </file>
@@ -383,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:B4"/>
+  <dimension ref="B2:B9"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
@@ -401,12 +414,50 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBEF4D3-FE80-457D-85FF-2615DD0F1119}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AB66E68-3299-4492-9EFF-4B8189BCB7DD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7E5DE5-58CA-4532-A316-FC4055D39363}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
@@ -462,13 +513,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FBEF4D3-FE80-457D-85FF-2615DD0F1119}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>